--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_249_R25.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_249_R25.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.0927</v>
+        <v>5.0614</v>
       </c>
       <c r="E2" t="n">
-        <v>9.3218</v>
+        <v>7.3913</v>
       </c>
       <c r="F2" t="n">
-        <v>-2.2291</v>
+        <v>-2.3299</v>
       </c>
       <c r="G2" t="n">
         <v>4.8735</v>
@@ -610,13 +610,13 @@
         <v>0.232</v>
       </c>
       <c r="S2" t="n">
-        <v>4.1316</v>
+        <v>2.1003</v>
       </c>
       <c r="T2" t="n">
-        <v>3.5583</v>
+        <v>1.6278</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5733</v>
+        <v>0.4725</v>
       </c>
       <c r="V2" t="n">
         <v>-2.1444</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.5956</v>
+        <v>3.5878</v>
       </c>
       <c r="E3" t="n">
-        <v>3.6599</v>
+        <v>4.7529</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.0643</v>
+        <v>-1.1652</v>
       </c>
       <c r="G3" t="n">
         <v>3.246</v>
@@ -688,13 +688,13 @@
         <v>1.6237</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.72</v>
+        <v>0.2721</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.0455</v>
+        <v>0.0474</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3255</v>
+        <v>0.2247</v>
       </c>
       <c r="V3" t="n">
         <v>-0.3943</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8622</v>
+        <v>1.6536</v>
       </c>
       <c r="E4" t="n">
-        <v>2.151</v>
+        <v>2.7407</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.2888</v>
+        <v>-1.0871</v>
       </c>
       <c r="G4" t="n">
         <v>3.0369</v>
@@ -766,13 +766,13 @@
         <v>0.9278</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.2469</v>
+        <v>0.5445</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0395</v>
+        <v>0.6293</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.2864</v>
+        <v>-0.0848</v>
       </c>
       <c r="V4" t="n">
         <v>-0.5361</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>C. MONEKE</t>
+          <t>J. NWORA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8289</v>
+        <v>0.7383</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9761</v>
+        <v>0.6556</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.1472</v>
+        <v>0.0827</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.3832</v>
+        <v>-2.4972</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.5606</v>
+        <v>0.3504</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1774</v>
+        <v>-2.8475</v>
       </c>
       <c r="J5" t="n">
-        <v>0.4001</v>
+        <v>-0.8812</v>
       </c>
       <c r="K5" t="n">
-        <v>0.3767</v>
+        <v>1.1735</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0234</v>
+        <v>-2.0547</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.7833</v>
+        <v>-1.616</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.9373</v>
+        <v>-0.8231000000000001</v>
       </c>
       <c r="O5" t="n">
-        <v>0.154</v>
+        <v>-0.7929</v>
       </c>
       <c r="P5" t="n">
+        <v>0.9278</v>
+      </c>
+      <c r="Q5" t="n">
         <v>-1.1598</v>
       </c>
-      <c r="Q5" t="n">
-        <v>-2.3195</v>
-      </c>
       <c r="R5" t="n">
-        <v>1.1598</v>
+        <v>2.0876</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9054</v>
+        <v>-0.2311</v>
       </c>
       <c r="T5" t="n">
-        <v>0.7512</v>
+        <v>0.016</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1542</v>
+        <v>-0.2471</v>
       </c>
       <c r="V5" t="n">
-        <v>1.4665</v>
+        <v>2.5387</v>
       </c>
       <c r="W5" t="n">
-        <v>2.1444</v>
+        <v>2.6805</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.6778999999999999</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>O. DOBRIC</t>
+          <t>C. MONEKE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7927</v>
+        <v>0.7088</v>
       </c>
       <c r="E6" t="n">
-        <v>0.218</v>
+        <v>0.8895999999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5747</v>
+        <v>-0.1808</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.0306</v>
+        <v>-0.3832</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6687</v>
+        <v>-0.5606</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.6993</v>
+        <v>0.1774</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.195</v>
+        <v>0.4001</v>
       </c>
       <c r="K6" t="n">
-        <v>0.5546</v>
+        <v>0.3767</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.7495000000000001</v>
+        <v>0.0234</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1644</v>
+        <v>-0.7833</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1141</v>
+        <v>-0.9373</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0502</v>
+        <v>0.154</v>
       </c>
       <c r="P6" t="n">
-        <v>0.232</v>
+        <v>-1.1598</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-2.3195</v>
       </c>
       <c r="R6" t="n">
-        <v>0.232</v>
+        <v>1.1598</v>
       </c>
       <c r="S6" t="n">
-        <v>0.5913</v>
+        <v>0.7852</v>
       </c>
       <c r="T6" t="n">
-        <v>0.4129</v>
+        <v>0.6647</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1784</v>
+        <v>0.1206</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.4665</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>2.1444</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.6778999999999999</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>N. KALINIC</t>
+          <t>O. DOBRIC</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5495</v>
+        <v>0.506</v>
       </c>
       <c r="E7" t="n">
-        <v>0.6533</v>
+        <v>-0.1359</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.1038</v>
+        <v>0.6419</v>
       </c>
       <c r="G7" t="n">
-        <v>1.0878</v>
+        <v>-0.0306</v>
       </c>
       <c r="H7" t="n">
-        <v>0.7264</v>
+        <v>0.6687</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3614</v>
+        <v>-0.6993</v>
       </c>
       <c r="J7" t="n">
-        <v>1.5669</v>
+        <v>-0.195</v>
       </c>
       <c r="K7" t="n">
-        <v>0.9915</v>
+        <v>0.5546</v>
       </c>
       <c r="L7" t="n">
-        <v>0.5754</v>
+        <v>-0.7495000000000001</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.4791</v>
+        <v>0.1644</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.2651</v>
+        <v>0.1141</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.214</v>
+        <v>0.0502</v>
       </c>
       <c r="P7" t="n">
         <v>0.232</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.3917</v>
+        <v>0.232</v>
       </c>
       <c r="S7" t="n">
-        <v>0.6963</v>
+        <v>0.3047</v>
       </c>
       <c r="T7" t="n">
-        <v>0.7512</v>
+        <v>0.0591</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0549</v>
+        <v>0.2456</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.4665</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.5051</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.9615</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. NWORA</t>
+          <t>N. KALINIC</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.3718</v>
+        <v>0.4459</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.5553</v>
+        <v>0.4488</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1835</v>
+        <v>-0.003</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.4972</v>
+        <v>1.0878</v>
       </c>
       <c r="H8" t="n">
-        <v>0.3504</v>
+        <v>0.7264</v>
       </c>
       <c r="I8" t="n">
-        <v>-2.8475</v>
+        <v>0.3614</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.8812</v>
+        <v>1.5669</v>
       </c>
       <c r="K8" t="n">
-        <v>1.1735</v>
+        <v>0.9915</v>
       </c>
       <c r="L8" t="n">
-        <v>-2.0547</v>
+        <v>0.5754</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.616</v>
+        <v>-0.4791</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.8231000000000001</v>
+        <v>-0.2651</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.7929</v>
+        <v>-0.214</v>
       </c>
       <c r="P8" t="n">
-        <v>0.9278</v>
+        <v>0.232</v>
       </c>
       <c r="Q8" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R8" t="n">
-        <v>2.0876</v>
+        <v>1.3917</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.3412</v>
+        <v>0.5926</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.1949</v>
+        <v>0.5467</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1463</v>
+        <v>0.0459</v>
       </c>
       <c r="V8" t="n">
-        <v>2.5387</v>
+        <v>-1.4665</v>
       </c>
       <c r="W8" t="n">
-        <v>2.6805</v>
+        <v>-0.5051</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.1418</v>
+        <v>-0.9615</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.9843</v>
+        <v>-0.2094</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.5985</v>
+        <v>-0.8908</v>
       </c>
       <c r="F9" t="n">
-        <v>0.6142</v>
+        <v>0.6814</v>
       </c>
       <c r="G9" t="n">
         <v>-0.7968</v>
@@ -1156,13 +1156,13 @@
         <v>0.6959</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.7415</v>
+        <v>0.0334</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5228</v>
+        <v>0.1849</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2188</v>
+        <v>-0.1516</v>
       </c>
       <c r="V9" t="n">
         <v>-0.1418</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.3065</v>
+        <v>-0.6673</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.0402</v>
+        <v>-0.8043</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2663</v>
+        <v>0.1369</v>
       </c>
       <c r="G10" t="n">
         <v>-1.7485</v>
@@ -1234,13 +1234,13 @@
         <v>1.1598</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.7178</v>
+        <v>-0.0786</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.0351</v>
+        <v>0.2008</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.6827</v>
+        <v>-0.2794</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.9201</v>
+        <v>-3.9392</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.8573</v>
+        <v>-3.3724</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.06279999999999999</v>
+        <v>-0.5669</v>
       </c>
       <c r="G12" t="n">
         <v>-0.9365</v>
@@ -1390,13 +1390,13 @@
         <v>1.8556</v>
       </c>
       <c r="S12" t="n">
-        <v>1.1066</v>
+        <v>0.08740000000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>0.6765</v>
+        <v>0.1614</v>
       </c>
       <c r="U12" t="n">
-        <v>0.4301</v>
+        <v>-0.074</v>
       </c>
       <c r="V12" t="n">
         <v>-1.4665</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.282900000000001</v>
+        <v>6.0299</v>
       </c>
       <c r="E13" t="n">
-        <v>9.544999999999996</v>
+        <v>10.2917</v>
       </c>
       <c r="F13" t="n">
-        <v>-4.2621</v>
+        <v>-4.2622</v>
       </c>
       <c r="G13" t="n">
         <v>5.1473</v>
@@ -1438,16 +1438,16 @@
         <v>4.8799</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2676000000000014</v>
+        <v>0.2676000000000001</v>
       </c>
       <c r="J13" t="n">
         <v>13.4592</v>
       </c>
       <c r="K13" t="n">
-        <v>8.424700000000001</v>
+        <v>8.4247</v>
       </c>
       <c r="L13" t="n">
-        <v>5.034599999999998</v>
+        <v>5.0346</v>
       </c>
       <c r="M13" t="n">
         <v>-8.3119</v>
@@ -1468,10 +1468,10 @@
         <v>11.5979</v>
       </c>
       <c r="S13" t="n">
-        <v>3.4398</v>
+        <v>4.1865</v>
       </c>
       <c r="T13" t="n">
-        <v>3.167299999999999</v>
+        <v>3.9141</v>
       </c>
       <c r="U13" t="n">
         <v>0.2724000000000001</v>
@@ -1480,7 +1480,7 @@
         <v>-2.1444</v>
       </c>
       <c r="W13" t="n">
-        <v>5.675599999999999</v>
+        <v>5.6756</v>
       </c>
       <c r="X13" t="n">
         <v>-7.8201</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>8.109500000000001</v>
+        <v>6.3079</v>
       </c>
       <c r="E14" t="n">
-        <v>10.4316</v>
+        <v>9.1341</v>
       </c>
       <c r="F14" t="n">
-        <v>-2.3221</v>
+        <v>-2.8262</v>
       </c>
       <c r="G14" t="n">
         <v>5.4511</v>
@@ -1546,13 +1546,13 @@
         <v>1.8556</v>
       </c>
       <c r="S14" t="n">
-        <v>1.429</v>
+        <v>-0.3725</v>
       </c>
       <c r="T14" t="n">
-        <v>1.3961</v>
+        <v>0.09859999999999999</v>
       </c>
       <c r="U14" t="n">
-        <v>0.033</v>
+        <v>-0.4711</v>
       </c>
       <c r="V14" t="n">
         <v>-0.3943</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.4145</v>
+        <v>3.4246</v>
       </c>
       <c r="E15" t="n">
-        <v>3.0659</v>
+        <v>3.7736</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.6514</v>
+        <v>-0.349</v>
       </c>
       <c r="G15" t="n">
         <v>1.7618</v>
@@ -1624,13 +1624,13 @@
         <v>2.0876</v>
       </c>
       <c r="S15" t="n">
-        <v>-2.2751</v>
+        <v>-1.265</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.8804</v>
+        <v>-0.1727</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.3948</v>
+        <v>-1.0923</v>
       </c>
       <c r="V15" t="n">
         <v>1.0722</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.022</v>
+        <v>0.7252</v>
       </c>
       <c r="E16" t="n">
-        <v>1.1959</v>
+        <v>0.1343</v>
       </c>
       <c r="F16" t="n">
-        <v>0.8260999999999999</v>
+        <v>0.5909</v>
       </c>
       <c r="G16" t="n">
         <v>0.4723</v>
@@ -1702,13 +1702,13 @@
         <v>0.6959</v>
       </c>
       <c r="S16" t="n">
-        <v>2.1038</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="T16" t="n">
-        <v>1.6948</v>
+        <v>0.6332</v>
       </c>
       <c r="U16" t="n">
-        <v>0.409</v>
+        <v>0.1737</v>
       </c>
       <c r="V16" t="n">
         <v>0.1418</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1637</v>
+        <v>0.7028</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.1031</v>
+        <v>0.3687</v>
       </c>
       <c r="F17" t="n">
-        <v>0.2668</v>
+        <v>0.334</v>
       </c>
       <c r="G17" t="n">
         <v>1.4231</v>
@@ -1780,13 +1780,13 @@
         <v>1.3917</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.5788</v>
+        <v>-1.0398</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.0297</v>
+        <v>-0.5579</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.5491</v>
+        <v>-0.4819</v>
       </c>
       <c r="V17" t="n">
         <v>-1.0722</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.6163</v>
+        <v>-0.4476</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.268</v>
+        <v>-0.0321</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.3483</v>
+        <v>-0.4155</v>
       </c>
       <c r="G18" t="n">
         <v>0.7254</v>
@@ -1858,13 +1858,13 @@
         <v>0.6959</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.6818</v>
+        <v>-0.5131</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.5149</v>
+        <v>-0.279</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1669</v>
+        <v>-0.2341</v>
       </c>
       <c r="V18" t="n">
         <v>-1.3558</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.8665</v>
+        <v>-0.8501</v>
       </c>
       <c r="E19" t="n">
-        <v>1.2359</v>
+        <v>1.118</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.1025</v>
+        <v>-1.968</v>
       </c>
       <c r="G19" t="n">
         <v>-2.7611</v>
@@ -1936,13 +1936,13 @@
         <v>2.0876</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.6572</v>
+        <v>-0.6407</v>
       </c>
       <c r="T19" t="n">
-        <v>0.08699999999999999</v>
+        <v>-0.031</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.7442</v>
+        <v>-0.6097</v>
       </c>
       <c r="V19" t="n">
         <v>3.2476</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.5215</v>
+        <v>-1.1011</v>
       </c>
       <c r="E20" t="n">
-        <v>0.0716</v>
+        <v>0.1896</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.5931</v>
+        <v>-1.2906</v>
       </c>
       <c r="G20" t="n">
         <v>-1.7699</v>
@@ -2014,13 +2014,13 @@
         <v>1.6237</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.6278</v>
+        <v>-0.2074</v>
       </c>
       <c r="T20" t="n">
-        <v>0.1142</v>
+        <v>0.2322</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.742</v>
+        <v>-0.4395</v>
       </c>
       <c r="V20" t="n">
         <v>-0.2836</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.7223</v>
+        <v>-1.1661</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.6824</v>
+        <v>-1.0927</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.0398</v>
+        <v>-0.0735</v>
       </c>
       <c r="G21" t="n">
         <v>-2.3082</v>
@@ -2092,13 +2092,13 @@
         <v>1.3917</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.4863</v>
+        <v>0.0698</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.8136</v>
+        <v>-0.2238</v>
       </c>
       <c r="U21" t="n">
-        <v>0.3273</v>
+        <v>0.2937</v>
       </c>
       <c r="V21" t="n">
         <v>1.0722</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-6.4926</v>
+        <v>-6.1052</v>
       </c>
       <c r="E24" t="n">
-        <v>-5.3605</v>
+        <v>-5.0066</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.1321</v>
+        <v>-1.0985</v>
       </c>
       <c r="G24" t="n">
         <v>-5.2987</v>
@@ -2326,13 +2326,13 @@
         <v>0.9278</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.3589</v>
+        <v>0.0286</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.1019</v>
+        <v>0.2519</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.257</v>
+        <v>-0.2234</v>
       </c>
       <c r="V24" t="n">
         <v>0.7886</v>
@@ -2359,10 +2359,10 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.2829</v>
+        <v>-5.283000000000001</v>
       </c>
       <c r="E25" t="n">
-        <v>5.334200000000001</v>
+        <v>5.334200000000002</v>
       </c>
       <c r="F25" t="n">
         <v>-10.6171</v>
@@ -2407,10 +2407,10 @@
         <v>-3.4398</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.2724999999999999</v>
+        <v>-0.2726000000000001</v>
       </c>
       <c r="U25" t="n">
-        <v>-3.1673</v>
+        <v>-3.1672</v>
       </c>
       <c r="V25" t="n">
         <v>2.144299999999999</v>
